--- a/Selenium_practice/Projects/data.xlsx
+++ b/Selenium_practice/Projects/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\Selenium_practice\Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\Selenium_practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8862FBA-FFE0-442F-A9D6-B9CFFB324158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAD82B3-1AB8-4A64-91B7-82926A01BC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{EE7DD0F4-58F3-4D05-BA64-FEB3777813BF}"/>
   </bookViews>
